--- a/Investments.xlsx
+++ b/Investments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ctimemt-my.sharepoint.com/personal/jpgalea_computime_com_mt/Documents/Documents/JP folder/Investments/Kathleen investments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{D8FFD0E9-07D3-40CD-9E37-AAD3A5438099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="14_{D8FFD0E9-07D3-40CD-9E37-AAD3A5438099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4610C23A-23DE-4DEB-A981-D9A178D3A6E5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{63AD4105-E52D-46FC-BCFA-6F1752685CAC}"/>
   </bookViews>
@@ -217,11 +217,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.00000000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,6 +250,14 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -281,7 +290,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,7 +319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -323,14 +332,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -818,7 +831,7 @@
         <f>K3/M3</f>
         <v>52.088265934274077</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3">
         <v>55</v>
       </c>
       <c r="L3" s="10">
@@ -847,18 +860,27 @@
       <c r="C4" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="16"/>
+      <c r="D4" s="17">
+        <v>3.01772879</v>
+      </c>
       <c r="F4" t="s">
         <v>11</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
+      </c>
+      <c r="H4" s="19">
+        <f>I4*M4</f>
+        <v>66.366600000000005</v>
+      </c>
+      <c r="I4" s="10">
+        <v>62.61</v>
       </c>
       <c r="J4">
         <f>K4/M4</f>
         <v>178.24528301886792</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4">
         <v>188.94</v>
       </c>
       <c r="L4" s="10">
@@ -887,7 +909,9 @@
       <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="16"/>
+      <c r="D5" s="18">
+        <v>8.8213E-2</v>
+      </c>
       <c r="E5"/>
       <c r="F5" t="s">
         <v>44</v>
@@ -895,6 +919,9 @@
       <c r="G5" t="s">
         <v>12</v>
       </c>
+      <c r="H5" s="19">
+        <v>2834.05</v>
+      </c>
       <c r="J5" s="10">
         <v>250</v>
       </c>
@@ -921,11 +948,17 @@
       <c r="C6" t="s">
         <v>16</v>
       </c>
+      <c r="D6" s="18">
+        <v>4.4772858299999996</v>
+      </c>
       <c r="F6" t="s">
         <v>33</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
+      </c>
+      <c r="H6" s="19">
+        <v>111.67</v>
       </c>
       <c r="J6" s="10">
         <v>500</v>
@@ -953,16 +986,22 @@
       <c r="C7" t="s">
         <v>7</v>
       </c>
+      <c r="D7" s="18">
+        <v>5.6710999999999998E-2</v>
+      </c>
       <c r="F7" t="s">
         <v>44</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="17">
+      <c r="H7" s="19">
+        <v>4364.6000000000004</v>
+      </c>
+      <c r="J7" s="16">
         <v>250</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="16">
         <v>2.48</v>
       </c>
       <c r="N7" t="s">
@@ -985,11 +1024,17 @@
       <c r="C8" t="s">
         <v>16</v>
       </c>
+      <c r="D8" s="18">
+        <v>2.2087018299999999</v>
+      </c>
       <c r="F8" t="s">
         <v>33</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
+      </c>
+      <c r="H8" s="19">
+        <v>112.74</v>
       </c>
       <c r="J8" s="10">
         <v>249.01</v>
@@ -1160,7 +1205,7 @@
       <c r="A4" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="16">
         <v>252.5</v>
       </c>
       <c r="D4" t="s">
@@ -1201,7 +1246,7 @@
       <c r="A6" s="1">
         <v>46057</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="16">
         <v>500</v>
       </c>
       <c r="D6" t="s">

--- a/Investments.xlsx
+++ b/Investments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ctimemt-my.sharepoint.com/personal/jpgalea_computime_com_mt/Documents/Documents/JP folder/Investments/Kathleen investments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="14_{D8FFD0E9-07D3-40CD-9E37-AAD3A5438099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4610C23A-23DE-4DEB-A981-D9A178D3A6E5}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="14_{D8FFD0E9-07D3-40CD-9E37-AAD3A5438099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A199130A-0AAD-440C-A3B3-ADE486D7E412}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{63AD4105-E52D-46FC-BCFA-6F1752685CAC}"/>
   </bookViews>
@@ -217,8 +217,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+  <numFmts count="2">
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000000"/>
   </numFmts>
@@ -319,7 +318,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -335,7 +334,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -343,7 +341,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -789,7 +786,7 @@
         <f>K2/M2</f>
         <v>49.70178926441352</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2">
         <v>55</v>
       </c>
       <c r="L2" s="12">
@@ -829,15 +826,15 @@
       </c>
       <c r="J3">
         <f>K3/M3</f>
-        <v>52.088265934274077</v>
+        <v>79.8655175679515</v>
       </c>
       <c r="K3">
-        <v>55</v>
+        <v>84.33</v>
       </c>
       <c r="L3" s="10">
         <v>0.01</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="13">
         <v>1.0559000000000001</v>
       </c>
       <c r="N3" t="s">
@@ -860,7 +857,7 @@
       <c r="C4" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>3.01772879</v>
       </c>
       <c r="F4" t="s">
@@ -869,7 +866,7 @@
       <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="10">
         <f>I4*M4</f>
         <v>66.366600000000005</v>
       </c>
@@ -886,7 +883,7 @@
       <c r="L4" s="10">
         <v>4.9800000000000004</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="13">
         <v>1.06</v>
       </c>
       <c r="N4" t="s">
@@ -909,7 +906,7 @@
       <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>8.8213E-2</v>
       </c>
       <c r="E5"/>
@@ -919,7 +916,7 @@
       <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="10">
         <v>2834.05</v>
       </c>
       <c r="J5" s="10">
@@ -948,7 +945,7 @@
       <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <v>4.4772858299999996</v>
       </c>
       <c r="F6" t="s">
@@ -957,7 +954,7 @@
       <c r="G6" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="10">
         <v>111.67</v>
       </c>
       <c r="J6" s="10">
@@ -986,7 +983,7 @@
       <c r="C7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>5.6710999999999998E-2</v>
       </c>
       <c r="F7" t="s">
@@ -995,13 +992,13 @@
       <c r="G7" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="10">
         <v>4364.6000000000004</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>250</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="15">
         <v>2.48</v>
       </c>
       <c r="N7" t="s">
@@ -1024,7 +1021,7 @@
       <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>2.2087018299999999</v>
       </c>
       <c r="F8" t="s">
@@ -1033,7 +1030,7 @@
       <c r="G8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="10">
         <v>112.74</v>
       </c>
       <c r="J8" s="10">
@@ -1179,7 +1176,7 @@
       <c r="A3" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="14">
         <v>119.87</v>
       </c>
       <c r="D3" t="s">
@@ -1205,7 +1202,7 @@
       <c r="A4" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="15">
         <v>252.5</v>
       </c>
       <c r="D4" t="s">
@@ -1246,7 +1243,7 @@
       <c r="A6" s="1">
         <v>46057</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="15">
         <v>500</v>
       </c>
       <c r="D6" t="s">

--- a/Investments.xlsx
+++ b/Investments.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ctimemt-my.sharepoint.com/personal/jpgalea_computime_com_mt/Documents/Documents/JP folder/Investments/Kathleen investments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="14_{D8FFD0E9-07D3-40CD-9E37-AAD3A5438099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A199130A-0AAD-440C-A3B3-ADE486D7E412}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{F9659319-8282-40A4-A744-6D44A79FC596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6F7E474-792D-4071-B325-0133357859D2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{63AD4105-E52D-46FC-BCFA-6F1752685CAC}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63AD4105-E52D-46FC-BCFA-6F1752685CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Transactions" sheetId="3" r:id="rId1"/>
     <sheet name="Introduced Capital" sheetId="5" r:id="rId2"/>
+    <sheet name="Income Received" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Transactions!$A$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Transactions!$A$1:$AA$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="91">
   <si>
     <t>Date</t>
   </si>
@@ -153,6 +154,12 @@
     <t>Cash</t>
   </si>
   <si>
+    <t>1SXP.DE</t>
+  </si>
+  <si>
+    <t>SCHOTT Pharma AG &amp; Co. KGaA</t>
+  </si>
+  <si>
     <t>% return (Investment.com)</t>
   </si>
   <si>
@@ -177,51 +184,148 @@
     <t>commodity</t>
   </si>
   <si>
+    <t>WDH1.HA</t>
+  </si>
+  <si>
+    <t>Total Euro Value Invested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">currency </t>
+  </si>
+  <si>
+    <t>FC Amount</t>
+  </si>
+  <si>
+    <t>FX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dividend </t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>Revolut</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Source Notes</t>
+  </si>
+  <si>
+    <t>Revolut Transactions</t>
+  </si>
+  <si>
+    <t>Revolut Bank Statement</t>
+  </si>
+  <si>
+    <t>Other Income Received from Investments - Enter here the Dividend income and the interest earned on Parked Funds</t>
+  </si>
+  <si>
+    <t>Parked cash</t>
+  </si>
+  <si>
+    <t>Intoduced</t>
+  </si>
+  <si>
+    <t>Net Return</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>FC</t>
+  </si>
+  <si>
+    <t>Cash Invested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parked Cash </t>
+  </si>
+  <si>
+    <t>Exit Reason</t>
+  </si>
+  <si>
+    <t>03.09.2024</t>
+  </si>
+  <si>
+    <t>Elastic</t>
+  </si>
+  <si>
+    <t>ESTC</t>
+  </si>
+  <si>
+    <t>04.12.2024</t>
+  </si>
+  <si>
+    <t>09.12.2024</t>
+  </si>
+  <si>
+    <t>The Coca-Cola Company</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>27.06.2025</t>
+  </si>
+  <si>
+    <t>29.01.2026</t>
+  </si>
+  <si>
+    <t>04.02.2026</t>
+  </si>
+  <si>
     <t>01.09.2024</t>
   </si>
   <si>
-    <t>03.09.2024</t>
-  </si>
-  <si>
-    <t>Elastic</t>
-  </si>
-  <si>
-    <t>04.12.2024</t>
-  </si>
-  <si>
     <t>07.12.2024</t>
   </si>
   <si>
-    <t>The Coca-Cola Company</t>
-  </si>
-  <si>
-    <t>KO</t>
-  </si>
-  <si>
-    <t>09.12.2024</t>
-  </si>
-  <si>
-    <t>ESTC</t>
-  </si>
-  <si>
-    <t>27.06.2025</t>
-  </si>
-  <si>
-    <t>29.01.2026</t>
-  </si>
-  <si>
-    <t>04.02.2026</t>
+    <t>27.03.2026</t>
+  </si>
+  <si>
+    <t>02.04.2026</t>
+  </si>
+  <si>
+    <t>06.04.2026</t>
+  </si>
+  <si>
+    <t>Transfer to USD Balance to Eur</t>
+  </si>
+  <si>
+    <t>$235.19</t>
+  </si>
+  <si>
+    <t>07.04.2026</t>
+  </si>
+  <si>
+    <t>Dermant</t>
+  </si>
+  <si>
+    <t>Prysmian Group</t>
+  </si>
+  <si>
+    <t>PRY.MI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000000"/>
+    <numFmt numFmtId="166" formatCode="[$€-2]\ #,##0.00;[Red]\-[$€-2]\ #,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,8 +350,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <u/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -261,8 +374,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -284,6 +405,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,10 +451,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -329,18 +461,28 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -677,7 +819,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF01DC48-F479-4579-898B-C21EE4D7B337}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:AA58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -690,98 +832,110 @@
     <col min="9" max="9" width="20.88671875" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="15.109375" customWidth="1"/>
-    <col min="16" max="17" width="16.88671875" customWidth="1"/>
-    <col min="18" max="18" width="12.5546875" customWidth="1"/>
-    <col min="19" max="19" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="16.88671875" customWidth="1"/>
+    <col min="20" max="20" width="12.5546875" customWidth="1"/>
+    <col min="21" max="21" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:27" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q1" s="6" t="s">
+      <c r="P1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="U1" s="7" t="s">
+      <c r="V1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="Y1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AA1" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="10">
+        <v>72</v>
+      </c>
+      <c r="D2" s="8">
         <v>1</v>
       </c>
+      <c r="E2" s="8"/>
       <c r="F2" t="s">
         <v>11</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
       <c r="J2">
         <f>K2/M2</f>
         <v>49.70178926441352</v>
@@ -789,10 +943,10 @@
       <c r="K2">
         <v>55</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="14">
         <v>0.78</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="14">
         <v>1.1066</v>
       </c>
       <c r="N2" t="s">
@@ -801,29 +955,37 @@
       <c r="O2" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="X2" s="11"/>
-    </row>
-    <row r="3" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P2">
+        <f t="shared" ref="P2:P4" si="0">IF(O2="Bought",-K2,K2)</f>
+        <v>-55</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" ref="Q2:Q4" si="1">IF(N2="Euro",(IF(AND(N2="EURO",O2="Bought"),-J2,J2)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="10">
+        <v>72</v>
+      </c>
+      <c r="D3" s="8">
         <v>1</v>
       </c>
+      <c r="E3" s="8"/>
       <c r="F3" t="s">
         <v>11</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
       </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
       <c r="J3">
         <f>K3/M3</f>
         <v>79.8655175679515</v>
@@ -831,46 +993,52 @@
       <c r="K3">
         <v>84.33</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="8">
         <v>0.01</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="15">
         <v>1.0559000000000001</v>
       </c>
       <c r="N3" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="X3" s="11"/>
-    </row>
-    <row r="4" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P3">
+        <f t="shared" si="0"/>
+        <v>84.33</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D4" s="16">
         <v>3.01772879</v>
       </c>
+      <c r="E4" s="8"/>
       <c r="F4" t="s">
         <v>11</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="8">
         <f>I4*M4</f>
         <v>66.366600000000005</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="8">
         <v>62.61</v>
       </c>
       <c r="J4">
@@ -880,10 +1048,10 @@
       <c r="K4">
         <v>188.94</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="8">
         <v>4.9800000000000004</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="15">
         <v>1.06</v>
       </c>
       <c r="N4" t="s">
@@ -892,13 +1060,18 @@
       <c r="O4" t="s">
         <v>18</v>
       </c>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="X4" s="11"/>
-    </row>
-    <row r="5" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P4">
+        <f t="shared" si="0"/>
+        <v>-188.94</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -909,35 +1082,42 @@
       <c r="D5" s="17">
         <v>8.8213E-2</v>
       </c>
-      <c r="E5"/>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="8">
         <v>2834.05</v>
       </c>
-      <c r="J5" s="10">
+      <c r="I5" s="8"/>
+      <c r="J5" s="8">
         <v>250</v>
       </c>
-      <c r="L5" s="10">
+      <c r="K5" s="8"/>
+      <c r="L5" s="8">
         <v>2.5</v>
       </c>
+      <c r="M5" s="8"/>
       <c r="N5" t="s">
         <v>14</v>
       </c>
       <c r="O5" t="s">
         <v>18</v>
       </c>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="X5" s="11"/>
-    </row>
-    <row r="6" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P5">
+        <f t="shared" ref="P5:P26" si="2">IF(O5="Bought",-K5,K5)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q26" si="3">IF(N5="Euro",(IF(AND(N5="EURO",O5="Bought"),-J5,J5)),0)</f>
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -948,34 +1128,43 @@
       <c r="D6" s="17">
         <v>4.4772858299999996</v>
       </c>
+      <c r="E6" s="8"/>
       <c r="F6" t="s">
         <v>33</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <v>111.67</v>
       </c>
-      <c r="J6" s="10">
+      <c r="I6" s="8"/>
+      <c r="J6" s="8">
         <v>500</v>
       </c>
-      <c r="L6" s="10">
-        <v>0</v>
-      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8"/>
       <c r="N6" t="s">
         <v>14</v>
       </c>
       <c r="O6" t="s">
         <v>18</v>
       </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="X6" s="11"/>
-    </row>
-    <row r="7" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="3"/>
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -986,34 +1175,43 @@
       <c r="D7" s="17">
         <v>5.6710999999999998E-2</v>
       </c>
+      <c r="E7" s="8"/>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="8">
         <v>4364.6000000000004</v>
       </c>
-      <c r="J7" s="15">
+      <c r="I7" s="8"/>
+      <c r="J7" s="18">
         <v>250</v>
       </c>
-      <c r="L7" s="15">
+      <c r="K7" s="8"/>
+      <c r="L7" s="18">
         <v>2.48</v>
       </c>
+      <c r="M7" s="8"/>
       <c r="N7" t="s">
         <v>14</v>
       </c>
       <c r="O7" t="s">
         <v>18</v>
       </c>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
-      <c r="X7" s="11"/>
-    </row>
-    <row r="8" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="3"/>
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -1024,77 +1222,691 @@
       <c r="D8" s="17">
         <v>2.2087018299999999</v>
       </c>
+      <c r="E8" s="8"/>
       <c r="F8" t="s">
         <v>33</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="8">
         <v>112.74</v>
       </c>
-      <c r="J8" s="10">
+      <c r="I8" s="8"/>
+      <c r="J8" s="8">
         <v>249.01</v>
       </c>
-      <c r="L8" s="10">
+      <c r="K8" s="8"/>
+      <c r="L8" s="8">
         <v>1</v>
       </c>
+      <c r="M8" s="8"/>
       <c r="N8" t="s">
         <v>14</v>
       </c>
       <c r="O8" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="11"/>
-      <c r="V8" s="11"/>
-      <c r="X8" s="11"/>
-    </row>
-    <row r="9" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="U9" s="11"/>
-      <c r="V9" s="11"/>
-      <c r="X9" s="11"/>
-    </row>
-    <row r="10" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="X10" s="11"/>
-    </row>
-    <row r="11" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="U11" s="11"/>
-      <c r="V11" s="11"/>
-      <c r="X11" s="11"/>
-    </row>
-    <row r="12" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="X12" s="11"/>
-    </row>
-    <row r="13" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="X13" s="11"/>
-    </row>
-    <row r="14" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="X14" s="11"/>
-    </row>
-    <row r="15" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="X15" s="11"/>
+      <c r="P8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="3"/>
+        <v>-249.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9">
+        <v>5.2815410600000003</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <v>94.48</v>
+      </c>
+      <c r="J9" s="20">
+        <v>499</v>
+      </c>
+      <c r="L9" s="20">
+        <v>1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>14</v>
+      </c>
+      <c r="O9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="3"/>
+        <v>-499</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="16">
+        <v>3.01772879</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10">
+        <f>I10/$M$10</f>
+        <v>66.446854663774403</v>
+      </c>
+      <c r="I10">
+        <v>76.58</v>
+      </c>
+      <c r="J10">
+        <f>K10/$M$10</f>
+        <v>200.52060737527114</v>
+      </c>
+      <c r="K10">
+        <v>231.1</v>
+      </c>
+      <c r="L10">
+        <f>1.16/M10</f>
+        <v>1.0065075921908893</v>
+      </c>
+      <c r="M10">
+        <v>1.1525000000000001</v>
+      </c>
+      <c r="N10" t="s">
+        <v>13</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="2"/>
+        <v>231.1</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11">
+        <v>19.12384969</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11">
+        <v>26.08</v>
+      </c>
+      <c r="J11">
+        <v>498.75</v>
+      </c>
+      <c r="L11">
+        <v>1.25</v>
+      </c>
+      <c r="N11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="3"/>
+        <v>-498.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="I12" s="20"/>
+      <c r="P12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="P13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="P14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="P15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="P16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="P24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="P25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="P26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="E27" s="20"/>
+      <c r="P27">
+        <f t="shared" ref="P27:P58" si="4">IF(O27="Bought",-K27,K27)</f>
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" ref="Q27:Q58" si="5">IF(N27="Euro",(IF(AND(N27="EURO",O27="Bought"),-J27,J27)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="E28" s="20"/>
+      <c r="P28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="E29" s="20"/>
+      <c r="P29">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="P30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="P31">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="P32">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="P33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="E34" s="20"/>
+      <c r="P34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="P35">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="P36">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P38">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P39">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P40">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P41">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P43">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P47">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="P48">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="16:17" x14ac:dyDescent="0.3">
+      <c r="P49">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="16:17" x14ac:dyDescent="0.3">
+      <c r="P50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="16:17" x14ac:dyDescent="0.3">
+      <c r="P51">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="16:17" x14ac:dyDescent="0.3">
+      <c r="P52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="16:17" x14ac:dyDescent="0.3">
+      <c r="P53">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="16:17" x14ac:dyDescent="0.3">
+      <c r="P54">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="16:17" x14ac:dyDescent="0.3">
+      <c r="P55">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="16:17" x14ac:dyDescent="0.3">
+      <c r="P56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="16:17" x14ac:dyDescent="0.3">
+      <c r="P57">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="16:17" x14ac:dyDescent="0.3">
+      <c r="P58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M15" xr:uid="{5E09A18B-ADDB-46AF-9CD2-AF496BA93A46}"/>
+  <autoFilter ref="A1:AA1" xr:uid="{BF01DC48-F479-4579-898B-C21EE4D7B337}"/>
   <hyperlinks>
-    <hyperlink ref="U1" r:id="rId1" display="https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/eurofxref-graph-usd.en.html" xr:uid="{1D3EFCC8-E459-454F-8A9D-8517EAC17B7B}"/>
-    <hyperlink ref="V1" r:id="rId2" display="https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/eurofxref-graph-gbp.en.html" xr:uid="{7FD5EB64-A6A2-46E1-A92F-970008DF62FC}"/>
-    <hyperlink ref="X1" r:id="rId3" xr:uid="{14FA0684-84D1-44A1-A986-A1EC55F966A8}"/>
+    <hyperlink ref="X1" r:id="rId1" display="https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/eurofxref-graph-usd.en.html" xr:uid="{1D3EFCC8-E459-454F-8A9D-8517EAC17B7B}"/>
+    <hyperlink ref="Y1" r:id="rId2" display="https://www.ecb.europa.eu/stats/policy_and_exchange_rates/euro_reference_exchange_rates/html/eurofxref-graph-gbp.en.html" xr:uid="{7FD5EB64-A6A2-46E1-A92F-970008DF62FC}"/>
+    <hyperlink ref="AA1" r:id="rId3" xr:uid="{14FA0684-84D1-44A1-A986-A1EC55F966A8}"/>
+    <hyperlink ref="C11" r:id="rId4" display="https://finance.yahoo.com/quote/WDH1.HA" xr:uid="{18ED0ED4-8FCE-46DA-B61A-C76287EF4881}"/>
+    <hyperlink ref="C9" r:id="rId5" display="https://finance.yahoo.com/quote/PRY.MI" xr:uid="{99F01E56-F61D-4421-A326-C80E7889423F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
   <customProperties>
-    <customPr name="QAA_DRILLPATH_NODE_ID" r:id="rId5"/>
+    <customPr name="QAA_DRILLPATH_NODE_ID" r:id="rId7"/>
   </customProperties>
 </worksheet>
 </file>
@@ -1102,7 +1914,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387B36C6-4A47-4E81-8B15-25CD3446FD0A}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -1112,47 +1924,47 @@
     <col min="13" max="13" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J1" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="O1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B2">
         <v>50.41</v>
@@ -1160,73 +1972,90 @@
       <c r="D2" t="s">
         <v>30</v>
       </c>
-      <c r="J2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2">
-        <f>SUMIF(D:D,J2,B:B)</f>
-        <v>1422.78</v>
-      </c>
-      <c r="M2">
-        <f>K2</f>
-        <v>1422.78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="14">
+        <v>81</v>
+      </c>
+      <c r="B3" s="19">
         <v>119.87</v>
       </c>
       <c r="D3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3">
-        <f>SUMIF(D:D,J3,E:E)</f>
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <f>SUMIF(D:D,J3,B:B)</f>
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <f>L3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>63</v>
+      </c>
+      <c r="R3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="15">
+        <v>77</v>
+      </c>
+      <c r="B4" s="18">
         <v>252.5</v>
       </c>
       <c r="D4" t="s">
         <v>30</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4">
-        <f>SUMIF(D:D,J4,E:E)</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
+        <v>30</v>
+      </c>
+      <c r="K4" s="9">
         <f>SUMIF(D:D,J4,B:B)</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="2">
-        <f>L4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1922.78</v>
+      </c>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9">
+        <f>K4</f>
+        <v>1922.78</v>
+      </c>
+      <c r="O4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P4" s="9">
+        <f>K4</f>
+        <v>1922.78</v>
+      </c>
+      <c r="Q4">
+        <f>SUMIF(Transactions!N:N,'Introduced Capital'!O4,Transactions!Q:Q)</f>
+        <v>-2246.7600000000002</v>
+      </c>
+      <c r="R4">
+        <f>SUMIF('Income Received'!E:E,O4,'Income Received'!H:H)</f>
+        <v>4.45</v>
+      </c>
+      <c r="S4" s="9">
+        <f>SUM(P4:R4)</f>
+        <v>-319.53000000000026</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="B5">
         <v>500</v>
@@ -1234,103 +2063,208 @@
       <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="M5">
-        <f>SUM(L11:L16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="9">
+        <f>SUMIF(D:D,J5,E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="9">
+        <f>SUMIF(D:D,J5,B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="9">
+        <f>L5</f>
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>13</v>
+      </c>
+      <c r="P5" s="9">
+        <f>K5</f>
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <f>SUMIF(Transactions!N:N,'Introduced Capital'!O5,Transactions!P:P)</f>
+        <v>71.489999999999981</v>
+      </c>
+      <c r="R5">
+        <f>SUMIF('Income Received'!E:E,O5,'Income Received'!F:F)</f>
+        <v>11.700000000000003</v>
+      </c>
+      <c r="S5" s="9">
+        <f>P5+Q5+R5</f>
+        <v>83.189999999999984</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46057</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="18">
         <v>500</v>
       </c>
       <c r="D6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="8">
-        <f>SUM(M2:M5)</f>
-        <v>1422.78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="9">
+        <f>SUMIF(D:D,J6,E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="9">
+        <f>SUMIF(D:D,J6,B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="9">
+        <f>L6</f>
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" s="9">
+        <f>K6</f>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f>SUMIF(Transactions!N:N,'Introduced Capital'!O6,Transactions!P:P)</f>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f>SUMIF('Income Received'!E:E,O6,'Income Received'!F:F)</f>
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="S6" s="9">
+        <f>P6+Q6+R6</f>
+        <v>1.7999999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="20">
+        <v>500</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="9">
+        <f>SUM(L12:L16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="20">
+        <v>297.32</v>
+      </c>
+      <c r="M8" s="9"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M9" s="9"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M10" s="9"/>
+    </row>
+    <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C11" s="3"/>
+      <c r="J11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11" s="10">
+        <f>SUM(M4:M7)</f>
+        <v>1922.78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="G25" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" t="s">
+        <v>85</v>
+      </c>
+      <c r="J25" s="20">
+        <v>202.68</v>
+      </c>
+      <c r="K25" s="20">
+        <v>202.68</v>
+      </c>
+      <c r="L25">
+        <v>1.1402000000000001</v>
+      </c>
+      <c r="M25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
@@ -1369,7 +2303,193 @@
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
     </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="O1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="QAA_DRILLPATH_NODE_ID" r:id="rId1"/>
+  </customProperties>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D69A77C-4F36-40A3-8F5F-AD4E886E82FF}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" customWidth="1"/>
+    <col min="11" max="11" width="27.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>4.45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <f>17.2904-5.5904</f>
+        <v>11.700000000000003</v>
+      </c>
+      <c r="G5">
+        <f>F5/H5</f>
+        <v>1.1669309715448373</v>
+      </c>
+      <c r="H5">
+        <f>14.8183-4.792</f>
+        <v>10.026300000000001</v>
+      </c>
+      <c r="J5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6">
+        <f>2.4179-0.6179</f>
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="G6">
+        <f>F6/H6</f>
+        <v>0.86650941125499437</v>
+      </c>
+      <c r="H6">
+        <f>2.7893-0.712</f>
+        <v>2.0773000000000001</v>
+      </c>
+      <c r="J6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <customProperties>
     <customPr name="QAA_DRILLPATH_NODE_ID" r:id="rId1"/>
@@ -1388,13 +2508,17 @@
       <SuppressZero>false</SuppressZero>
       <Children/>
     </DrillPathNode>
+    <DrillPathNode AnalysisType="NONE" Id="4c6486de-e1db-478d-80cf-0dc32579e066" Name="Income Received" HandleSummaryReportOnly="false" Source="">
+      <SuppressZero>false</SuppressZero>
+      <Children/>
+    </DrillPathNode>
   </CurrentDrillPath>
   <SavedDrillPath/>
 </WorkbookDrillPathInfo>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5B1827E-D7D6-4163-91B8-2D92E005576C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4517BE73-17D9-4421-87A8-E19F5756707D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.infor.com/qaa/DrillPath"/>
